--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9531,0.0077,0.0205,0.0040</t>
-  </si>
-  <si>
-    <t>0.9630,0.0052,0.0073,0.0082</t>
-  </si>
-  <si>
-    <t>0.9292,0.0158,0.0138,0.0158</t>
-  </si>
-  <si>
-    <t>0.9835,0.0025,0.0027,0.0034</t>
-  </si>
-  <si>
-    <t>0.5978,0.2964,0.0097,0.0178</t>
-  </si>
-  <si>
-    <t>0.9320,0.0526,0.0032,0.0028</t>
-  </si>
-  <si>
-    <t>0.9404,0.0266,0.0027,0.0032</t>
-  </si>
-  <si>
-    <t>0.9497,0.0141,0.0011,0.0042</t>
-  </si>
-  <si>
-    <t>0.9706,0.0171,0.0011,0.0015</t>
-  </si>
-  <si>
-    <t>0.9046,0.0470,0.0068,0.0084</t>
-  </si>
-  <si>
-    <t>0.9054,0.0392,0.0188,0.0156</t>
-  </si>
-  <si>
-    <t>0.9464,0.0653,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.9956,0.0010,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.8968,0.0982,0.0088,0.0006</t>
-  </si>
-  <si>
-    <t>0.9923,0.0023,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9898,0.0022,0.0051,0.0001</t>
-  </si>
-  <si>
-    <t>0.9847,0.0067,0.0030,0.0005</t>
-  </si>
-  <si>
-    <t>0.3212,0.7672,0.0029,0.0011</t>
-  </si>
-  <si>
-    <t>0.4838,0.5663,0.0138,0.0026</t>
-  </si>
-  <si>
-    <t>0.8793,0.1000,0.0112,0.0016</t>
-  </si>
-  <si>
-    <t>0.5125,0.6376,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.0529,0.9549,0.0050,0.0013</t>
-  </si>
-  <si>
-    <t>0.9864,0.0018,0.0083,0.0006</t>
-  </si>
-  <si>
-    <t>0.9846,0.0038,0.0083,0.0002</t>
-  </si>
-  <si>
-    <t>0.9715,0.0061,0.0163,0.0006</t>
-  </si>
-  <si>
-    <t>0.9862,0.0033,0.0077,0.0004</t>
-  </si>
-  <si>
-    <t>0.9881,0.0027,0.0065,0.0001</t>
-  </si>
-  <si>
-    <t>0.9737,0.0043,0.0288,0.0002</t>
-  </si>
-  <si>
-    <t>0.9721,0.0016,0.0493,0.0001</t>
-  </si>
-  <si>
-    <t>0.8720,0.1469,0.0049,0.0007</t>
-  </si>
-  <si>
-    <t>0.9498,0.0391,0.0074,0.0011</t>
-  </si>
-  <si>
-    <t>0.2886,0.2311,0.5890,0.0033</t>
-  </si>
-  <si>
-    <t>0.9776,0.0185,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.8996,0.0826,0.0130,0.0022</t>
-  </si>
-  <si>
-    <t>0.9445,0.0725,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.9268,0.0841,0.0032,0.0006</t>
-  </si>
-  <si>
-    <t>0.8602,0.1971,0.0029,0.0004</t>
-  </si>
-  <si>
-    <t>0.0773,0.8636,0.4993,0.0035</t>
-  </si>
-  <si>
-    <t>0.9073,0.0221,0.1096,0.0046</t>
-  </si>
-  <si>
-    <t>0.8233,0.0367,0.1789,0.0021</t>
-  </si>
-  <si>
-    <t>0.9669,0.0069,0.0229,0.0026</t>
-  </si>
-  <si>
-    <t>0.9822,0.0036,0.0110,0.0003</t>
-  </si>
-  <si>
-    <t>0.6406,0.3990,0.0480,0.0017</t>
-  </si>
-  <si>
-    <t>0.9879,0.0023,0.0063,0.0003</t>
-  </si>
-  <si>
-    <t>0.8346,0.1141,0.0198,0.0092</t>
-  </si>
-  <si>
-    <t>0.4779,0.5591,0.0164,0.0013</t>
-  </si>
-  <si>
-    <t>0.5783,0.6224,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.2300,0.8368,0.0117,0.0011</t>
-  </si>
-  <si>
-    <t>0.6629,0.0346,0.4975,0.0012</t>
-  </si>
-  <si>
-    <t>0.6880,0.0229,0.5356,0.0024</t>
-  </si>
-  <si>
-    <t>0.9869,0.0020,0.0103,0.0001</t>
-  </si>
-  <si>
-    <t>0.8670,0.0168,0.1541,0.0012</t>
-  </si>
-  <si>
-    <t>0.8483,0.0181,0.2132,0.0027</t>
-  </si>
-  <si>
-    <t>0.9774,0.0080,0.0107,0.0002</t>
-  </si>
-  <si>
-    <t>0.9502,0.0512,0.0031,0.0011</t>
-  </si>
-  <si>
-    <t>0.8799,0.1078,0.0047,0.0031</t>
-  </si>
-  <si>
-    <t>0.9081,0.1150,0.0021,0.0008</t>
-  </si>
-  <si>
-    <t>0.2395,0.5797,0.5043,0.0245</t>
-  </si>
-  <si>
-    <t>0.9591,0.0180,0.0023,0.0040</t>
-  </si>
-  <si>
-    <t>0.9479,0.0295,0.0043,0.0054</t>
-  </si>
-  <si>
-    <t>0.9123,0.0604,0.0030,0.0024</t>
-  </si>
-  <si>
-    <t>0.0828,0.7900,0.5803,0.0059</t>
-  </si>
-  <si>
-    <t>0.3073,0.0521,0.7950,0.0005</t>
-  </si>
-  <si>
-    <t>0.9586,0.0028,0.0855,0.0009</t>
-  </si>
-  <si>
-    <t>0.3391,0.6156,0.1699,0.0029</t>
-  </si>
-  <si>
-    <t>0.4651,0.0343,0.6693,0.0024</t>
-  </si>
-  <si>
-    <t>0.8580,0.2024,0.0042,0.0002</t>
-  </si>
-  <si>
-    <t>0.6631,0.6192,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9808,0.0099,0.0024,0.0006</t>
-  </si>
-  <si>
-    <t>0.9773,0.0127,0.0052,0.0002</t>
-  </si>
-  <si>
-    <t>0.1636,0.2893,0.6203,0.0012</t>
-  </si>
-  <si>
-    <t>0.5293,0.2823,0.1530,0.0007</t>
-  </si>
-  <si>
-    <t>0.1898,0.6918,0.3118,0.0023</t>
-  </si>
-  <si>
-    <t>0.1643,0.7972,0.1736,0.0005</t>
-  </si>
-  <si>
-    <t>0.0289,0.8875,0.6089,0.0015</t>
-  </si>
-  <si>
-    <t>0.9002,0.0109,0.0726,0.0190</t>
-  </si>
-  <si>
-    <t>0.9124,0.0261,0.0217,0.0116</t>
-  </si>
-  <si>
-    <t>0.9845,0.0016,0.0086,0.0015</t>
-  </si>
-  <si>
-    <t>0.9765,0.0081,0.0076,0.0013</t>
-  </si>
-  <si>
-    <t>0.9502,0.0075,0.0109,0.0093</t>
-  </si>
-  <si>
-    <t>0.9817,0.0037,0.0045,0.0022</t>
-  </si>
-  <si>
-    <t>0.5169,0.4177,0.1056,0.0008</t>
-  </si>
-  <si>
-    <t>0.7194,0.0504,0.3491,0.0039</t>
-  </si>
-  <si>
-    <t>0.8230,0.0229,0.2221,0.0009</t>
-  </si>
-  <si>
-    <t>0.4379,0.4242,0.1891,0.0016</t>
-  </si>
-  <si>
-    <t>0.0563,0.8709,0.4102,0.0009</t>
-  </si>
-  <si>
-    <t>0.5258,0.3433,0.1322,0.0022</t>
-  </si>
-  <si>
-    <t>0.9604,0.0350,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9422,0.0479,0.0066,0.0025</t>
-  </si>
-  <si>
-    <t>0.9135,0.0515,0.0095,0.0084</t>
-  </si>
-  <si>
-    <t>0.9412,0.0226,0.0036,0.0081</t>
-  </si>
-  <si>
-    <t>0.9576,0.0178,0.0058,0.0044</t>
-  </si>
-  <si>
-    <t>0.8737,0.0252,0.0017,0.0191</t>
-  </si>
-  <si>
-    <t>0.8425,0.1334,0.0020,0.0017</t>
-  </si>
-  <si>
-    <t>0.8400,0.0892,0.0054,0.0104</t>
-  </si>
-  <si>
-    <t>0.8188,0.0873,0.0176,0.0202</t>
-  </si>
-  <si>
-    <t>0.8822,0.0525,0.0022,0.0093</t>
-  </si>
-  <si>
-    <t>0.7841,0.1454,0.0165,0.0153</t>
-  </si>
-  <si>
-    <t>0.7051,0.1985,0.0082,0.0073</t>
-  </si>
-  <si>
-    <t>0.8538,0.0393,0.0065,0.0344</t>
-  </si>
-  <si>
-    <t>0.9070,0.0670,0.0053,0.0065</t>
-  </si>
-  <si>
-    <t>0.8215,0.1558,0.0093,0.0042</t>
-  </si>
-  <si>
-    <t>0.9441,0.0334,0.0051,0.0036</t>
-  </si>
-  <si>
-    <t>0.6679,0.0821,0.3444,0.0066</t>
-  </si>
-  <si>
-    <t>0.9658,0.0122,0.0106,0.0010</t>
-  </si>
-  <si>
-    <t>0.9877,0.0023,0.0047,0.0007</t>
-  </si>
-  <si>
-    <t>0.8949,0.0499,0.0307,0.0025</t>
-  </si>
-  <si>
-    <t>0.5102,0.6151,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.6493,0.3746,0.0103,0.0037</t>
-  </si>
-  <si>
-    <t>0.5547,0.5881,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.4352,0.7150,0.0048,0.0005</t>
-  </si>
-  <si>
-    <t>0.1256,0.9107,0.0024,0.0009</t>
-  </si>
-  <si>
-    <t>0.1319,0.9060,0.0058,0.0013</t>
-  </si>
-  <si>
-    <t>0.8571,0.1700,0.0086,0.0012</t>
-  </si>
-  <si>
-    <t>0.9899,0.0019,0.0039,0.0004</t>
-  </si>
-  <si>
-    <t>0.9930,0.0009,0.0035,0.0003</t>
-  </si>
-  <si>
-    <t>0.9774,0.0097,0.0051,0.0002</t>
-  </si>
-  <si>
-    <t>0.9888,0.0030,0.0033,0.0002</t>
-  </si>
-  <si>
-    <t>0.9956,0.0015,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.8048,0.2729,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.3231,0.7134,0.0058,0.0028</t>
-  </si>
-  <si>
-    <t>0.5413,0.5595,0.0027,0.0004</t>
-  </si>
-  <si>
-    <t>0.2392,0.8317,0.0141,0.0003</t>
-  </si>
-  <si>
-    <t>0.8503,0.1834,0.0031,0.0010</t>
-  </si>
-  <si>
-    <t>0.9495,0.0490,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.9005,0.1421,0.0039,0.0005</t>
-  </si>
-  <si>
-    <t>0.9227,0.0760,0.0077,0.0023</t>
-  </si>
-  <si>
-    <t>0.9370,0.0518,0.0053,0.0027</t>
-  </si>
-  <si>
-    <t>0.7360,0.1760,0.0030,0.0087</t>
-  </si>
-  <si>
-    <t>0.7587,0.2691,0.0044,0.0011</t>
-  </si>
-  <si>
-    <t>0.9298,0.0410,0.0102,0.0081</t>
-  </si>
-  <si>
-    <t>0.9812,0.0158,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.9371,0.0411,0.0023,0.0019</t>
-  </si>
-  <si>
-    <t>0.9663,0.0178,0.0017,0.0023</t>
-  </si>
-  <si>
-    <t>0.0328,0.8654,0.5037,0.0013</t>
-  </si>
-  <si>
-    <t>0.8075,0.1668,0.0406,0.0007</t>
-  </si>
-  <si>
-    <t>0.8411,0.0311,0.1720,0.0017</t>
-  </si>
-  <si>
-    <t>0.3946,0.4670,0.2787,0.0089</t>
-  </si>
-  <si>
-    <t>0.9812,0.0028,0.0129,0.0005</t>
-  </si>
-  <si>
-    <t>0.9932,0.0027,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9554,0.0242,0.0081,0.0011</t>
-  </si>
-  <si>
-    <t>0.9645,0.0260,0.0063,0.0005</t>
-  </si>
-  <si>
-    <t>0.9154,0.0156,0.0166,0.0169</t>
-  </si>
-  <si>
-    <t>0.9390,0.0106,0.0110,0.0148</t>
-  </si>
-  <si>
-    <t>0.9425,0.0053,0.0220,0.0176</t>
-  </si>
-  <si>
-    <t>0.9772,0.0019,0.0047,0.0056</t>
-  </si>
-  <si>
-    <t>0.4258,0.2558,0.4550,0.0079</t>
-  </si>
-  <si>
-    <t>0.9304,0.0324,0.0092,0.0072</t>
-  </si>
-  <si>
-    <t>0.7333,0.2534,0.0393,0.0035</t>
-  </si>
-  <si>
-    <t>0.9359,0.0441,0.0041,0.0026</t>
-  </si>
-  <si>
-    <t>0.5885,0.4218,0.0160,0.0047</t>
-  </si>
-  <si>
-    <t>0.9776,0.0087,0.0020,0.0014</t>
-  </si>
-  <si>
-    <t>0.9689,0.0126,0.0056,0.0016</t>
-  </si>
-  <si>
-    <t>0.9238,0.0335,0.0036,0.0049</t>
-  </si>
-  <si>
-    <t>0.1386,0.5752,0.6609,0.0422</t>
-  </si>
-  <si>
-    <t>0.9467,0.0408,0.0041,0.0011</t>
-  </si>
-  <si>
-    <t>0.9651,0.0211,0.0034,0.0013</t>
-  </si>
-  <si>
-    <t>0.7693,0.1894,0.0168,0.0037</t>
-  </si>
-  <si>
-    <t>0.8911,0.0940,0.0034,0.0012</t>
-  </si>
-  <si>
-    <t>0.9874,0.0093,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9525,0.0521,0.0033,0.0004</t>
-  </si>
-  <si>
-    <t>0.9762,0.0102,0.0069,0.0005</t>
-  </si>
-  <si>
-    <t>0.9961,0.0015,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.6908,0.2768,0.0052,0.0025</t>
-  </si>
-  <si>
-    <t>0.9306,0.0341,0.0025,0.0058</t>
-  </si>
-  <si>
-    <t>0.9720,0.0130,0.0008,0.0018</t>
-  </si>
-  <si>
-    <t>0.8861,0.0742,0.0025,0.0019</t>
-  </si>
-  <si>
-    <t>0.9072,0.0318,0.0179,0.0177</t>
-  </si>
-  <si>
-    <t>0.9318,0.0443,0.0059,0.0050</t>
-  </si>
-  <si>
-    <t>0.8929,0.0619,0.0193,0.0137</t>
-  </si>
-  <si>
-    <t>0.9375,0.0473,0.0042,0.0026</t>
-  </si>
-  <si>
-    <t>0.6705,0.4655,0.0054,0.0003</t>
-  </si>
-  <si>
-    <t>0.3705,0.6597,0.0206,0.0057</t>
-  </si>
-  <si>
-    <t>0.9190,0.0845,0.0029,0.0008</t>
-  </si>
-  <si>
-    <t>0.9501,0.0237,0.0036,0.0020</t>
-  </si>
-  <si>
-    <t>0.8753,0.1658,0.0026,0.0008</t>
-  </si>
-  <si>
-    <t>0.7767,0.0895,0.0023,0.0086</t>
-  </si>
-  <si>
-    <t>0.9548,0.0274,0.0058,0.0025</t>
-  </si>
-  <si>
-    <t>0.8872,0.0985,0.0060,0.0022</t>
-  </si>
-  <si>
-    <t>0.0996,0.5589,0.6815,0.0042</t>
-  </si>
-  <si>
-    <t>0.9748,0.0147,0.0025,0.0011</t>
-  </si>
-  <si>
-    <t>0.7344,0.1392,0.1084,0.0032</t>
-  </si>
-  <si>
-    <t>0.9381,0.0093,0.0589,0.0012</t>
-  </si>
-  <si>
-    <t>0.9567,0.0042,0.0706,0.0008</t>
-  </si>
-  <si>
-    <t>0.0503,0.7971,0.7816,0.0017</t>
-  </si>
-  <si>
-    <t>0.8247,0.1279,0.0357,0.0009</t>
-  </si>
-  <si>
-    <t>0.9656,0.0044,0.0449,0.0003</t>
-  </si>
-  <si>
-    <t>0.9711,0.0043,0.0334,0.0006</t>
-  </si>
-  <si>
-    <t>0.9601,0.0317,0.0047,0.0001</t>
-  </si>
-  <si>
-    <t>0.9871,0.0039,0.0051,0.0003</t>
-  </si>
-  <si>
-    <t>0.9703,0.0074,0.0162,0.0005</t>
-  </si>
-  <si>
-    <t>0.9719,0.0138,0.0052,0.0006</t>
-  </si>
-  <si>
-    <t>0.9840,0.0103,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9434,0.0219,0.0132,0.0029</t>
-  </si>
-  <si>
-    <t>0.9902,0.0030,0.0029,0.0004</t>
-  </si>
-  <si>
-    <t>0.9680,0.0208,0.0037,0.0004</t>
-  </si>
-  <si>
-    <t>0.7420,0.2153,0.0016,0.0033</t>
-  </si>
-  <si>
-    <t>0.7949,0.2661,0.0017,0.0017</t>
-  </si>
-  <si>
-    <t>0.9747,0.0169,0.0029,0.0011</t>
-  </si>
-  <si>
-    <t>0.8207,0.1032,0.0063,0.0146</t>
-  </si>
-  <si>
-    <t>0.6950,0.2854,0.0029,0.0035</t>
-  </si>
-  <si>
-    <t>0.9627,0.0275,0.0033,0.0004</t>
-  </si>
-  <si>
-    <t>0.9743,0.0050,0.0139,0.0007</t>
-  </si>
-  <si>
-    <t>0.9848,0.0017,0.0085,0.0011</t>
-  </si>
-  <si>
-    <t>0.9966,0.0008,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9931,0.0017,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.7432,0.0330,0.2642,0.0022</t>
-  </si>
-  <si>
-    <t>0.9239,0.0317,0.0224,0.0016</t>
-  </si>
-  <si>
-    <t>0.9275,0.0221,0.0658,0.0015</t>
-  </si>
-  <si>
-    <t>0.9476,0.0123,0.0381,0.0013</t>
-  </si>
-  <si>
-    <t>0.5683,0.2443,0.2376,0.0064</t>
-  </si>
-  <si>
-    <t>0.7174,0.1794,0.0070,0.0107</t>
-  </si>
-  <si>
-    <t>0.9112,0.0807,0.0039,0.0023</t>
-  </si>
-  <si>
-    <t>0.9623,0.0210,0.0020,0.0025</t>
-  </si>
-  <si>
-    <t>0.9516,0.0408,0.0029,0.0015</t>
-  </si>
-  <si>
-    <t>0.9436,0.0501,0.0014,0.0009</t>
-  </si>
-  <si>
-    <t>0.8921,0.0609,0.0086,0.0102</t>
-  </si>
-  <si>
-    <t>0.9321,0.0617,0.0047,0.0026</t>
-  </si>
-  <si>
-    <t>0.9074,0.0675,0.0050,0.0032</t>
-  </si>
-  <si>
-    <t>0.9840,0.0075,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9282,0.0634,0.0055,0.0008</t>
-  </si>
-  <si>
-    <t>0.9064,0.0743,0.0174,0.0013</t>
-  </si>
-  <si>
-    <t>0.7299,0.0593,0.2604,0.0009</t>
-  </si>
-  <si>
-    <t>0.7766,0.0330,0.3085,0.0028</t>
-  </si>
-  <si>
-    <t>0.8054,0.1105,0.0500,0.0010</t>
-  </si>
-  <si>
-    <t>0.7593,0.0254,0.3551,0.0009</t>
-  </si>
-  <si>
-    <t>0.9083,0.0282,0.0553,0.0003</t>
-  </si>
-  <si>
-    <t>0.1903,0.0372,0.8812,0.0042</t>
-  </si>
-  <si>
-    <t>0.9221,0.0156,0.0670,0.0032</t>
-  </si>
-  <si>
-    <t>0.9863,0.0031,0.0073,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0003,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9764,0.0084,0.0139,0.0004</t>
-  </si>
-  <si>
-    <t>0.9837,0.0030,0.0034,0.0017</t>
-  </si>
-  <si>
-    <t>0.9681,0.0201,0.0025,0.0012</t>
-  </si>
-  <si>
-    <t>0.9605,0.0290,0.0039,0.0013</t>
-  </si>
-  <si>
-    <t>0.9275,0.0486,0.0033,0.0038</t>
-  </si>
-  <si>
-    <t>0.9445,0.0347,0.0011,0.0027</t>
-  </si>
-  <si>
-    <t>0.9597,0.0260,0.0037,0.0025</t>
-  </si>
-  <si>
-    <t>0.9042,0.0971,0.0035,0.0017</t>
-  </si>
-  <si>
-    <t>0.9043,0.0809,0.0051,0.0023</t>
-  </si>
-  <si>
-    <t>0.9518,0.0329,0.0034,0.0026</t>
-  </si>
-  <si>
-    <t>0.9747,0.0134,0.0068,0.0002</t>
-  </si>
-  <si>
-    <t>0.8606,0.0266,0.1007,0.0004</t>
-  </si>
-  <si>
-    <t>0.7013,0.0200,0.3500,0.0008</t>
-  </si>
-  <si>
-    <t>0.9801,0.0032,0.0191,0.0003</t>
-  </si>
-  <si>
-    <t>0.9802,0.0023,0.0225,0.0002</t>
-  </si>
-  <si>
-    <t>0.9952,0.0011,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.9329,0.0235,0.0480,0.0011</t>
-  </si>
-  <si>
-    <t>0.9256,0.0176,0.0243,0.0091</t>
-  </si>
-  <si>
-    <t>0.9666,0.0063,0.0162,0.0028</t>
-  </si>
-  <si>
-    <t>0.9355,0.0159,0.0330,0.0078</t>
-  </si>
-  <si>
-    <t>0.9772,0.0043,0.0100,0.0017</t>
-  </si>
-  <si>
-    <t>0.9743,0.0010,0.0088,0.0040</t>
-  </si>
-  <si>
-    <t>0.9809,0.0008,0.0024,0.0060</t>
-  </si>
-  <si>
-    <t>0.9322,0.0302,0.0289,0.0029</t>
+    <t>0.5525,0.0455,0.0077,0.4044</t>
+  </si>
+  <si>
+    <t>0.0911,0.0008,0.0009,0.9673</t>
+  </si>
+  <si>
+    <t>0.3353,0.0073,0.0023,0.7757</t>
+  </si>
+  <si>
+    <t>0.0238,0.0144,0.0009,0.9801</t>
+  </si>
+  <si>
+    <t>0.9931,0.0016,0.0020,0.0018</t>
+  </si>
+  <si>
+    <t>0.9967,0.0006,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9913,0.0013,0.0004,0.0041</t>
+  </si>
+  <si>
+    <t>0.9967,0.0002,0.0002,0.0022</t>
+  </si>
+  <si>
+    <t>0.9858,0.0065,0.0008,0.0031</t>
+  </si>
+  <si>
+    <t>0.9929,0.0037,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9943,0.0013,0.0012,0.0017</t>
+  </si>
+  <si>
+    <t>0.9943,0.0023,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9264,0.0062,0.0785,0.0027</t>
+  </si>
+  <si>
+    <t>0.3213,0.0026,0.8260,0.0005</t>
+  </si>
+  <si>
+    <t>0.7112,0.0769,0.1601,0.0010</t>
+  </si>
+  <si>
+    <t>0.0251,0.0089,0.9610,0.0010</t>
+  </si>
+  <si>
+    <t>0.8120,0.0171,0.1973,0.0068</t>
+  </si>
+  <si>
+    <t>0.0006,0.9984,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.0945,0.9356,0.0021,0.0015</t>
+  </si>
+  <si>
+    <t>0.0471,0.9725,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0370,0.9752,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.0028,0.9959,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.5034,0.0019,0.4638,0.0328</t>
+  </si>
+  <si>
+    <t>0.8322,0.0024,0.3070,0.0018</t>
+  </si>
+  <si>
+    <t>0.0003,0.0032,0.9924,0.0116</t>
+  </si>
+  <si>
+    <t>0.4912,0.0062,0.5958,0.0017</t>
+  </si>
+  <si>
+    <t>0.0566,0.0076,0.9538,0.0044</t>
+  </si>
+  <si>
+    <t>0.0534,0.0064,0.9310,0.0174</t>
+  </si>
+  <si>
+    <t>0.0037,0.0006,0.9927,0.0027</t>
+  </si>
+  <si>
+    <t>0.4478,0.7094,0.0056,0.0010</t>
+  </si>
+  <si>
+    <t>0.8418,0.1098,0.0521,0.0190</t>
+  </si>
+  <si>
+    <t>0.0005,0.0015,0.9959,0.0094</t>
+  </si>
+  <si>
+    <t>0.0214,0.8989,0.0747,0.0038</t>
+  </si>
+  <si>
+    <t>0.9229,0.0628,0.0124,0.0126</t>
+  </si>
+  <si>
+    <t>0.9829,0.0069,0.0054,0.0009</t>
+  </si>
+  <si>
+    <t>0.8666,0.1874,0.0081,0.0012</t>
+  </si>
+  <si>
+    <t>0.0057,0.9775,0.2264,0.0009</t>
+  </si>
+  <si>
+    <t>0.0469,0.3087,0.5599,0.0565</t>
+  </si>
+  <si>
+    <t>0.3021,0.0067,0.7398,0.0168</t>
+  </si>
+  <si>
+    <t>0.0834,0.0235,0.9353,0.0048</t>
+  </si>
+  <si>
+    <t>0.2837,0.0040,0.6989,0.0233</t>
+  </si>
+  <si>
+    <t>0.0251,0.0344,0.9646,0.0016</t>
+  </si>
+  <si>
+    <t>0.0088,0.9318,0.0598,0.0035</t>
+  </si>
+  <si>
+    <t>0.0114,0.0090,0.9763,0.0035</t>
+  </si>
+  <si>
+    <t>0.7843,0.0617,0.0175,0.1446</t>
+  </si>
+  <si>
+    <t>0.0075,0.9843,0.0069,0.0143</t>
+  </si>
+  <si>
+    <t>0.0014,0.9919,0.0283,0.0012</t>
+  </si>
+  <si>
+    <t>0.0005,0.9978,0.0092,0.0002</t>
+  </si>
+  <si>
+    <t>0.0033,0.0068,0.9929,0.0018</t>
+  </si>
+  <si>
+    <t>0.0007,0.2167,0.9941,0.0007</t>
+  </si>
+  <si>
+    <t>0.0119,0.0098,0.9511,0.0405</t>
+  </si>
+  <si>
+    <t>0.0061,0.0028,0.9871,0.0048</t>
+  </si>
+  <si>
+    <t>0.0024,0.0125,0.9924,0.0035</t>
+  </si>
+  <si>
+    <t>0.0124,0.0229,0.9768,0.0009</t>
+  </si>
+  <si>
+    <t>0.9127,0.1589,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.9850,0.0027,0.0037,0.0047</t>
+  </si>
+  <si>
+    <t>0.9847,0.0063,0.0074,0.0016</t>
+  </si>
+  <si>
+    <t>0.0019,0.0274,0.9898,0.0047</t>
+  </si>
+  <si>
+    <t>0.9895,0.0058,0.0036,0.0016</t>
+  </si>
+  <si>
+    <t>0.9978,0.0013,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9939,0.0045,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.0033,0.6607,0.9547,0.0015</t>
+  </si>
+  <si>
+    <t>0.0115,0.1146,0.9864,0.0014</t>
+  </si>
+  <si>
+    <t>0.0049,0.0048,0.9920,0.0024</t>
+  </si>
+  <si>
+    <t>0.0008,0.9449,0.8845,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.0045,0.9966,0.0005</t>
+  </si>
+  <si>
+    <t>0.0154,0.9617,0.0498,0.0018</t>
+  </si>
+  <si>
+    <t>0.0196,0.9860,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9766,0.0043,0.0371,0.0008</t>
+  </si>
+  <si>
+    <t>0.1074,0.2413,0.8036,0.0020</t>
+  </si>
+  <si>
+    <t>0.0009,0.0257,0.9945,0.0026</t>
+  </si>
+  <si>
+    <t>0.0045,0.8917,0.6156,0.0009</t>
+  </si>
+  <si>
+    <t>0.0089,0.8296,0.3856,0.0022</t>
+  </si>
+  <si>
+    <t>0.0005,0.9947,0.1041,0.0008</t>
+  </si>
+  <si>
+    <t>0.0010,0.9816,0.5286,0.0001</t>
+  </si>
+  <si>
+    <t>0.0076,0.0006,0.0319,0.9832</t>
+  </si>
+  <si>
+    <t>0.0028,0.0014,0.0082,0.9955</t>
+  </si>
+  <si>
+    <t>0.0097,0.0023,0.0003,0.9951</t>
+  </si>
+  <si>
+    <t>0.0439,0.0008,0.0044,0.9749</t>
+  </si>
+  <si>
+    <t>0.0056,0.0031,0.0098,0.9924</t>
+  </si>
+  <si>
+    <t>0.0015,0.0190,0.0012,0.9969</t>
+  </si>
+  <si>
+    <t>0.0007,0.8815,0.9388,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.8191,0.9806,0.0002</t>
+  </si>
+  <si>
+    <t>0.0171,0.6371,0.2924,0.0264</t>
+  </si>
+  <si>
+    <t>0.0060,0.1163,0.9760,0.0012</t>
+  </si>
+  <si>
+    <t>0.0008,0.9470,0.7583,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.5962,0.9260,0.0009</t>
+  </si>
+  <si>
+    <t>0.9969,0.0006,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9966,0.0039,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9908,0.0047,0.0016,0.0016</t>
+  </si>
+  <si>
+    <t>0.9880,0.0060,0.0022,0.0016</t>
+  </si>
+  <si>
+    <t>0.9932,0.0032,0.0009,0.0017</t>
+  </si>
+  <si>
+    <t>0.9916,0.0029,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.9880,0.0071,0.0032,0.0018</t>
+  </si>
+  <si>
+    <t>0.9928,0.0055,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.9970,0.0006,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9964,0.0015,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9972,0.0004,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9934,0.0008,0.0004,0.0036</t>
+  </si>
+  <si>
+    <t>0.9930,0.0044,0.0033,0.0007</t>
+  </si>
+  <si>
+    <t>0.9948,0.0005,0.0001,0.0032</t>
+  </si>
+  <si>
+    <t>0.9951,0.0005,0.0005,0.0034</t>
+  </si>
+  <si>
+    <t>0.0149,0.0011,0.9896,0.0016</t>
+  </si>
+  <si>
+    <t>0.0494,0.0386,0.9305,0.0061</t>
+  </si>
+  <si>
+    <t>0.9291,0.0076,0.0456,0.0096</t>
+  </si>
+  <si>
+    <t>0.0068,0.0201,0.9807,0.0069</t>
+  </si>
+  <si>
+    <t>0.1288,0.9142,0.0013,0.0019</t>
+  </si>
+  <si>
+    <t>0.0085,0.9918,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.1320,0.9162,0.0008,0.0017</t>
+  </si>
+  <si>
+    <t>0.0971,0.9344,0.0039,0.0015</t>
+  </si>
+  <si>
+    <t>0.0418,0.9757,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.0160,0.9739,0.0123,0.0048</t>
+  </si>
+  <si>
+    <t>0.6306,0.4883,0.0038,0.0022</t>
+  </si>
+  <si>
+    <t>0.9542,0.0068,0.0406,0.0024</t>
+  </si>
+  <si>
+    <t>0.1955,0.0096,0.7744,0.0319</t>
+  </si>
+  <si>
+    <t>0.0880,0.3923,0.5390,0.0900</t>
+  </si>
+  <si>
+    <t>0.1559,0.0321,0.7612,0.0661</t>
+  </si>
+  <si>
+    <t>0.7328,0.0315,0.1807,0.0871</t>
+  </si>
+  <si>
+    <t>0.0042,0.9862,0.0224,0.0018</t>
+  </si>
+  <si>
+    <t>0.0042,0.9815,0.0114,0.0030</t>
+  </si>
+  <si>
+    <t>0.0004,0.9981,0.0020,0.0047</t>
+  </si>
+  <si>
+    <t>0.0068,0.9011,0.2763,0.0023</t>
+  </si>
+  <si>
+    <t>0.0106,0.9896,0.0077,0.0001</t>
+  </si>
+  <si>
+    <t>0.7922,0.2852,0.0103,0.0005</t>
+  </si>
+  <si>
+    <t>0.8850,0.1585,0.0079,0.0007</t>
+  </si>
+  <si>
+    <t>0.9918,0.0037,0.0028,0.0015</t>
+  </si>
+  <si>
+    <t>0.9963,0.0006,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9926,0.0013,0.0010,0.0023</t>
+  </si>
+  <si>
+    <t>0.9769,0.0089,0.0087,0.0039</t>
+  </si>
+  <si>
+    <t>0.9948,0.0005,0.0011,0.0022</t>
+  </si>
+  <si>
+    <t>0.9941,0.0022,0.0039,0.0004</t>
+  </si>
+  <si>
+    <t>0.9921,0.0023,0.0028,0.0018</t>
+  </si>
+  <si>
+    <t>0.9855,0.0044,0.0024,0.0043</t>
+  </si>
+  <si>
+    <t>0.0065,0.4443,0.9335,0.0021</t>
+  </si>
+  <si>
+    <t>0.0031,0.9121,0.7733,0.0008</t>
+  </si>
+  <si>
+    <t>0.0123,0.2048,0.8574,0.0050</t>
+  </si>
+  <si>
+    <t>0.0041,0.5081,0.9819,0.0008</t>
+  </si>
+  <si>
+    <t>0.9550,0.0109,0.0229,0.0028</t>
+  </si>
+  <si>
+    <t>0.6783,0.0013,0.2915,0.0169</t>
+  </si>
+  <si>
+    <t>0.2599,0.0021,0.8001,0.0114</t>
+  </si>
+  <si>
+    <t>0.6398,0.0530,0.3701,0.0324</t>
+  </si>
+  <si>
+    <t>0.2231,0.0015,0.0010,0.9129</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.0004,0.9996</t>
+  </si>
+  <si>
+    <t>0.0024,0.0021,0.0045,0.9966</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.0030,0.9984</t>
+  </si>
+  <si>
+    <t>0.0022,0.8852,0.5764,0.0020</t>
+  </si>
+  <si>
+    <t>0.9908,0.0037,0.0022,0.0021</t>
+  </si>
+  <si>
+    <t>0.1643,0.8804,0.0016,0.0071</t>
+  </si>
+  <si>
+    <t>0.9975,0.0008,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.7815,0.3520,0.0023,0.0013</t>
+  </si>
+  <si>
+    <t>0.9735,0.0056,0.0047,0.0140</t>
+  </si>
+  <si>
+    <t>0.4825,0.0027,0.0029,0.6665</t>
+  </si>
+  <si>
+    <t>0.9911,0.0016,0.0018,0.0025</t>
+  </si>
+  <si>
+    <t>0.0023,0.0067,0.9864,0.0214</t>
+  </si>
+  <si>
+    <t>0.6875,0.0007,0.0026,0.4597</t>
+  </si>
+  <si>
+    <t>0.9100,0.0058,0.0468,0.0279</t>
+  </si>
+  <si>
+    <t>0.7100,0.2962,0.0343,0.0061</t>
+  </si>
+  <si>
+    <t>0.8625,0.0389,0.0031,0.0500</t>
+  </si>
+  <si>
+    <t>0.9951,0.0043,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.2423,0.7478,0.0124,0.0307</t>
+  </si>
+  <si>
+    <t>0.7059,0.0492,0.2326,0.0199</t>
+  </si>
+  <si>
+    <t>0.9807,0.0096,0.0076,0.0010</t>
+  </si>
+  <si>
+    <t>0.9889,0.0025,0.0012,0.0040</t>
+  </si>
+  <si>
+    <t>0.9959,0.0019,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9963,0.0009,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9958,0.0003,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9928,0.0027,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.9806,0.0141,0.0013,0.0029</t>
+  </si>
+  <si>
+    <t>0.9935,0.0010,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.9728,0.0579,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9527,0.0729,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.7874,0.2699,0.0030,0.0019</t>
+  </si>
+  <si>
+    <t>0.9388,0.0234,0.0374,0.0231</t>
+  </si>
+  <si>
+    <t>0.9925,0.0041,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.9506,0.0485,0.0069,0.0037</t>
+  </si>
+  <si>
+    <t>0.9918,0.0046,0.0014,0.0012</t>
+  </si>
+  <si>
+    <t>0.9812,0.0128,0.0023,0.0034</t>
+  </si>
+  <si>
+    <t>0.0004,0.0139,0.9977,0.0009</t>
+  </si>
+  <si>
+    <t>0.9709,0.0163,0.0111,0.0017</t>
+  </si>
+  <si>
+    <t>0.0004,0.0210,0.9931,0.0013</t>
+  </si>
+  <si>
+    <t>0.0461,0.3090,0.8518,0.0041</t>
+  </si>
+  <si>
+    <t>0.0411,0.0043,0.9623,0.0035</t>
+  </si>
+  <si>
+    <t>0.0020,0.3870,0.9914,0.0009</t>
+  </si>
+  <si>
+    <t>0.0032,0.0190,0.9882,0.0020</t>
+  </si>
+  <si>
+    <t>0.0073,0.0338,0.9655,0.0160</t>
+  </si>
+  <si>
+    <t>0.0016,0.0019,0.9941,0.0046</t>
+  </si>
+  <si>
+    <t>0.1539,0.0267,0.8343,0.0105</t>
+  </si>
+  <si>
+    <t>0.0603,0.4132,0.3805,0.1262</t>
+  </si>
+  <si>
+    <t>0.0182,0.0744,0.9401,0.0071</t>
+  </si>
+  <si>
+    <t>0.1102,0.0106,0.8913,0.0009</t>
+  </si>
+  <si>
+    <t>0.2747,0.0676,0.5661,0.0014</t>
+  </si>
+  <si>
+    <t>0.1361,0.1686,0.6180,0.0167</t>
+  </si>
+  <si>
+    <t>0.7420,0.0221,0.2282,0.0468</t>
+  </si>
+  <si>
+    <t>0.1282,0.0380,0.7633,0.0667</t>
+  </si>
+  <si>
+    <t>0.9471,0.0410,0.0090,0.0007</t>
+  </si>
+  <si>
+    <t>0.9131,0.1475,0.0036,0.0013</t>
+  </si>
+  <si>
+    <t>0.9769,0.0266,0.0041,0.0014</t>
+  </si>
+  <si>
+    <t>0.9837,0.0182,0.0020,0.0010</t>
+  </si>
+  <si>
+    <t>0.7330,0.4252,0.0032,0.0034</t>
+  </si>
+  <si>
+    <t>0.8781,0.0266,0.0746,0.0086</t>
+  </si>
+  <si>
+    <t>0.9630,0.0034,0.0316,0.0036</t>
+  </si>
+  <si>
+    <t>0.8112,0.0027,0.0922,0.0337</t>
+  </si>
+  <si>
+    <t>0.8946,0.0053,0.1306,0.0042</t>
+  </si>
+  <si>
+    <t>0.4884,0.0221,0.4184,0.0623</t>
+  </si>
+  <si>
+    <t>0.0117,0.0063,0.9638,0.0227</t>
+  </si>
+  <si>
+    <t>0.0139,0.1844,0.9299,0.0134</t>
+  </si>
+  <si>
+    <t>0.0313,0.0828,0.9469,0.0102</t>
+  </si>
+  <si>
+    <t>0.6023,0.0034,0.6212,0.0003</t>
+  </si>
+  <si>
+    <t>0.0109,0.1502,0.8386,0.0047</t>
+  </si>
+  <si>
+    <t>0.9874,0.0040,0.0019,0.0050</t>
+  </si>
+  <si>
+    <t>0.9951,0.0014,0.0009,0.0013</t>
+  </si>
+  <si>
+    <t>0.9861,0.0098,0.0036,0.0016</t>
+  </si>
+  <si>
+    <t>0.9914,0.0031,0.0073,0.0005</t>
+  </si>
+  <si>
+    <t>0.9759,0.0249,0.0029,0.0025</t>
+  </si>
+  <si>
+    <t>0.9931,0.0038,0.0036,0.0005</t>
+  </si>
+  <si>
+    <t>0.9853,0.0056,0.0019,0.0040</t>
+  </si>
+  <si>
+    <t>0.9970,0.0006,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.0030,0.0124,0.9860,0.0130</t>
+  </si>
+  <si>
+    <t>0.1574,0.3397,0.6475,0.0161</t>
+  </si>
+  <si>
+    <t>0.9692,0.0103,0.0156,0.0040</t>
+  </si>
+  <si>
+    <t>0.0021,0.0037,0.9932,0.0031</t>
+  </si>
+  <si>
+    <t>0.0018,0.0338,0.9800,0.0073</t>
+  </si>
+  <si>
+    <t>0.0071,0.1134,0.9624,0.0081</t>
+  </si>
+  <si>
+    <t>0.0010,0.0010,0.9980,0.0005</t>
+  </si>
+  <si>
+    <t>0.0092,0.0210,0.9729,0.0013</t>
+  </si>
+  <si>
+    <t>0.0017,0.0006,0.9978,0.0004</t>
+  </si>
+  <si>
+    <t>0.0502,0.0400,0.9228,0.0086</t>
+  </si>
+  <si>
+    <t>0.0217,0.3827,0.7818,0.0068</t>
+  </si>
+  <si>
+    <t>0.8531,0.0114,0.1141,0.0265</t>
+  </si>
+  <si>
+    <t>0.7801,0.0005,0.3832,0.0025</t>
+  </si>
+  <si>
+    <t>0.7822,0.0289,0.2539,0.0148</t>
+  </si>
+  <si>
+    <t>0.9865,0.0093,0.0027,0.0024</t>
+  </si>
+  <si>
+    <t>0.9958,0.0019,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9923,0.0022,0.0015,0.0027</t>
+  </si>
+  <si>
+    <t>0.9828,0.0073,0.0129,0.0012</t>
+  </si>
+  <si>
+    <t>0.9974,0.0005,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9940,0.0042,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9970,0.0007,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9946,0.0015,0.0012,0.0018</t>
+  </si>
+  <si>
+    <t>0.0078,0.0073,0.9846,0.0010</t>
+  </si>
+  <si>
+    <t>0.0045,0.0581,0.9813,0.0018</t>
+  </si>
+  <si>
+    <t>0.0091,0.0069,0.9837,0.0026</t>
+  </si>
+  <si>
+    <t>0.0316,0.0024,0.9663,0.0025</t>
+  </si>
+  <si>
+    <t>0.0158,0.0006,0.9863,0.0019</t>
+  </si>
+  <si>
+    <t>0.0564,0.0908,0.7770,0.2466</t>
+  </si>
+  <si>
+    <t>0.2256,0.0049,0.8604,0.0027</t>
+  </si>
+  <si>
+    <t>0.0861,0.0370,0.8727,0.0253</t>
+  </si>
+  <si>
+    <t>0.2866,0.0002,0.0014,0.8584</t>
+  </si>
+  <si>
+    <t>0.1321,0.0039,0.0078,0.9283</t>
+  </si>
+  <si>
+    <t>0.1957,0.0022,0.0010,0.9195</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0011,0.9994</t>
+  </si>
+  <si>
+    <t>0.0032,0.0001,0.0001,0.9987</t>
+  </si>
+  <si>
+    <t>0.9637,0.0073,0.0067,0.0140</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1981,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
         <v>266</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3395,7 +3395,7 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D105" t="s">
         <v>367</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3577,7 +3577,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
         <v>380</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5103,7 +5103,7 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D227" t="s">
         <v>489</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5439,7 +5439,7 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
         <v>513</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
